--- a/outputs/hard_cheese/silpo/primary_chain_output.xlsx
+++ b/outputs/hard_cheese/silpo/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001649183941800067</v>
+        <v>0.001649183941799371</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
       </c>
       <c r="D2" t="n">
-        <v>1.66813437649029e-12</v>
+        <v>1.668134376491154e-12</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>4.160589056408487e-21</v>
+        <v>4.160589056408666e-21</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -574,13 +574,13 @@
         <v>0.08893253878307611</v>
       </c>
       <c r="D3" t="n">
-        <v>1.532473806067052e-08</v>
+        <v>1.532473806066898e-08</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.196556730323243e-10</v>
+        <v>1.196556730322677e-10</v>
       </c>
       <c r="G3" t="n">
         <v>0.04166666666668085</v>
@@ -630,7 +630,7 @@
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>2.88926658174579e-06</v>
+        <v>2.889266581745764e-06</v>
       </c>
       <c r="G4" t="n">
         <v>0.1</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.2322700832601339</v>
+        <v>0.232270083260134</v>
       </c>
       <c r="N5" t="n">
         <v>189</v>
@@ -942,22 +942,22 @@
         <v>187</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.901684280673745</v>
+        <v>-1.901684280673758</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3195396559542991</v>
+        <v>0.3195396559542992</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.703887241265392</v>
+        <v>-0.7038872412653931</v>
       </c>
       <c r="M2" t="n">
-        <v>2.747609431022365e-15</v>
+        <v>2.747609431018937e-15</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1625343111972001</v>
+        <v>0.1625343111971972</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2610022514748195</v>
+        <v>0.2610022514748128</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
@@ -1024,10 +1024,10 @@
         <v>38</v>
       </c>
       <c r="J3" t="n">
-        <v>1.045350879786881</v>
+        <v>1.045350879786895</v>
       </c>
       <c r="K3" t="n">
-        <v>16.32664882022445</v>
+        <v>16.32664882021111</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -1098,22 +1098,22 @@
         <v>36</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03093538709143862</v>
+        <v>0.03093538709143831</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01877747610695744</v>
+        <v>0.01877747610695752</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.131301223411889</v>
+        <v>-1.13130122341189</v>
       </c>
       <c r="M4" t="n">
-        <v>2.544235929587362e-08</v>
+        <v>2.544235928732543e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8109745337593639</v>
+        <v>0.8109745337593635</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9240474765408485</v>
+        <v>0.9240474765408409</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3045392670214256</v>
+        <v>0.3045392670214253</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2688968463348229</v>
+        <v>0.2688968463348201</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05424410826903407</v>
+        <v>0.05424410826903467</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1247,13 +1247,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.644080315519358</v>
+        <v>0.2211502569416363</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002471109442311297</v>
+        <v>0.1839160470828664</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4999098230155331</v>
+        <v>0.4999098230155283</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5136560684499863</v>
+        <v>0.5136560684500009</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2221837447850576</v>
+        <v>0.2221837447850724</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -57301,10 +57301,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.852886918113318</v>
+        <v>-1.852886918113325</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04879736256042733</v>
+        <v>0.04879736256043321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -57317,10 +57317,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.52011630994642</v>
+        <v>-1.520116309946426</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04003356383238164</v>
+        <v>0.04003356383238646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -57333,10 +57333,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.579880495540932</v>
+        <v>-1.579880495540938</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04160750480205159</v>
+        <v>0.04160750480205661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -57349,10 +57349,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.56914710204969</v>
+        <v>-1.569147102049695</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04132483169956718</v>
+        <v>0.04132483169957216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -57365,10 +57365,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.571074773860019</v>
+        <v>-1.571074773860025</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04137559858625983</v>
+        <v>0.04137559858626482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -57381,10 +57381,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.570728572203351</v>
+        <v>-1.570728572203357</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04136648106937615</v>
+        <v>0.04136648106938114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -57397,10 +57397,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.57079074854812</v>
+        <v>-1.570790748548125</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04136811853662183</v>
+        <v>0.04136811853662681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -57413,10 +57413,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.570779581941102</v>
+        <v>-1.570779581941108</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04136782445447042</v>
+        <v>0.04136782445447541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -57429,10 +57429,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.570781587416219</v>
+        <v>-1.570781587416225</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04136787727037376</v>
+        <v>0.04136787727037875</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -57445,10 +57445,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.57078122724142</v>
+        <v>-1.570781227241425</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04136786778486221</v>
+        <v>0.04136786778486719</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -57461,10 +57461,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.570781291927281</v>
+        <v>-1.570781291927287</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04136786948841973</v>
+        <v>0.04136786948842472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -57477,10 +57477,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.570781280309976</v>
+        <v>-1.570781280309981</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04136786918246804</v>
+        <v>0.04136786918247303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57493,10 +57493,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.570781282396394</v>
+        <v>-1.5707812823964</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04136786923741567</v>
+        <v>0.04136786923742065</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -57509,10 +57509,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.570781282021682</v>
+        <v>-1.570781282021688</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04136786922754731</v>
+        <v>0.04136786922755229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -57525,10 +57525,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.570781282088979</v>
+        <v>-1.570781282088985</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04136786922931962</v>
+        <v>0.04136786922932461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -57541,10 +57541,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.570781282076893</v>
+        <v>-1.570781282076898</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04136786922900132</v>
+        <v>0.04136786922900631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -57557,10 +57557,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.570781282079064</v>
+        <v>-1.570781282079069</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04136786922905849</v>
+        <v>0.04136786922906347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -57573,10 +57573,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.570781282078674</v>
+        <v>-1.570781282078679</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04136786922904822</v>
+        <v>0.04136786922905321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -57589,10 +57589,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.570781282078744</v>
+        <v>-1.570781282078749</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04136786922905007</v>
+        <v>0.04136786922905505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -57605,10 +57605,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.570781282078731</v>
+        <v>-1.570781282078737</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04136786922904973</v>
+        <v>0.04136786922905472</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -57621,10 +57621,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.570781282078733</v>
+        <v>-1.570781282078739</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04136786922904979</v>
+        <v>0.04136786922905478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -57637,10 +57637,10 @@
         <v>0</v>
       </c>
       <c r="B23" t="n">
-        <v>0.134724732208544</v>
+        <v>0.1347247322085431</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1037893451171054</v>
+        <v>0.1037893451171047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -57653,10 +57653,10 @@
         <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1516516804232605</v>
+        <v>0.1516516804232596</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1168295407904367</v>
+        <v>0.1168295407904361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -57669,10 +57669,10 @@
         <v>2</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1537783988896233</v>
+        <v>0.1537783988896224</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1184679238345431</v>
+        <v>0.1184679238345425</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -57685,10 +57685,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1540456018950201</v>
+        <v>0.1540456018950192</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1186737718959111</v>
+        <v>0.1186737718959106</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -57701,10 +57701,10 @@
         <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1540791735441228</v>
+        <v>0.154079173544122</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1186996348493404</v>
+        <v>0.1186996348493398</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -57717,10 +57717,10 @@
         <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1540833915192231</v>
+        <v>0.1540833915192223</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1187028842963142</v>
+        <v>0.1187028842963137</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -57733,10 +57733,10 @@
         <v>6</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1540839214697743</v>
+        <v>0.1540839214697735</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1187032925600365</v>
+        <v>0.1187032925600359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -57749,10 +57749,10 @@
         <v>7</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1540839880532842</v>
+        <v>0.1540839880532833</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1187033438546932</v>
+        <v>0.1187033438546926</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -57765,10 +57765,10 @@
         <v>8</v>
       </c>
       <c r="B31" t="n">
-        <v>0.154083996418902</v>
+        <v>0.1540839964189012</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1187033502994044</v>
+        <v>0.1187033502994039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -57781,10 +57781,10 @@
         <v>9</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1540839974699665</v>
+        <v>0.1540839974699656</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1187033511091243</v>
+        <v>0.1187033511091237</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -57797,10 +57797,10 @@
         <v>10</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1540839976020233</v>
+        <v>0.1540839976020224</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1187033512108583</v>
+        <v>0.1187033512108577</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -57813,10 +57813,10 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>0.154083997618615</v>
+        <v>0.1540839976186142</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1187033512236403</v>
+        <v>0.1187033512236397</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -57829,10 +57829,10 @@
         <v>12</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1540839976206996</v>
+        <v>0.1540839976206987</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1187033512252462</v>
+        <v>0.1187033512252456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -57845,10 +57845,10 @@
         <v>13</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1540839976209615</v>
+        <v>0.1540839976209607</v>
       </c>
       <c r="C36" t="n">
-        <v>0.118703351225448</v>
+        <v>0.1187033512254474</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -57861,10 +57861,10 @@
         <v>14</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1540839976209945</v>
+        <v>0.1540839976209936</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1187033512254733</v>
+        <v>0.1187033512254728</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -57877,10 +57877,10 @@
         <v>15</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1540839976209986</v>
+        <v>0.1540839976209977</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1187033512254765</v>
+        <v>0.1187033512254759</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -57893,10 +57893,10 @@
         <v>16</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1540839976209991</v>
+        <v>0.1540839976209982</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1187033512254769</v>
+        <v>0.1187033512254763</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -57909,10 +57909,10 @@
         <v>17</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1540839976209992</v>
+        <v>0.1540839976209983</v>
       </c>
       <c r="C40" t="n">
-        <v>0.118703351225477</v>
+        <v>0.1187033512254764</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -57925,10 +57925,10 @@
         <v>18</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1540839976209992</v>
+        <v>0.1540839976209983</v>
       </c>
       <c r="C41" t="n">
-        <v>0.118703351225477</v>
+        <v>0.1187033512254764</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -57941,10 +57941,10 @@
         <v>19</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1540839976209992</v>
+        <v>0.1540839976209983</v>
       </c>
       <c r="C42" t="n">
-        <v>0.118703351225477</v>
+        <v>0.1187033512254764</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -57957,10 +57957,10 @@
         <v>20</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1540839976209992</v>
+        <v>0.1540839976209983</v>
       </c>
       <c r="C43" t="n">
-        <v>0.118703351225477</v>
+        <v>0.1187033512254764</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
